--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\SEPLAG\2022\SPLOR\DCPPN\LeiOrcamentariaAnual\LOA\bancos\SISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C606DEF-77D2-4CEF-975B-7CFC89EDC2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7AB0DD1-2AF4-4608-9F54-4D32C0BCECC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="150" windowWidth="21600" windowHeight="11145"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_QDD_PLURIANUAL_INVEST" sheetId="1" r:id="rId1"/>
@@ -1101,7 +1101,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1,43 +1,288 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_QDD_PLURIANUAL_INVEST" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BASE_QDD_PLURIANUAL_INVEST" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+  <si>
+    <t xml:space="preserve">ANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_ORGAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESC_ORGAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_UO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESC_UO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBFUNCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_PROGRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENT_PROJATIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJ_ATIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBPROJETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR (R$) 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR (R$) 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR (R$) 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR (R$) 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAÇÃO DE VALOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOIO ÀS POLÍTICAS PÚBLICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE SANEAMENTO DE MINAS GERAIS  - COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP SISTEMA ADUTOR RIO MANSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS CEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESENVOLVIMENTO SOCIOECONÔMICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL  DO BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +290,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -182,10 +350,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -211,15 +375,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -245,6 +406,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -420,140 +582,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>COD_ORGAO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DESC_ORGAO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>COD_UO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DESC_UO</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FUNCAO</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SUBFUNCAO</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>COD_PROGRAMA</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>IDENT_PROJATIV</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>PROJ_ATIV</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>AÇÃO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>SUBPROJETO</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FONTE</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>PROGRAMA</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ACAO</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR (R$) 2024</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR (R$) 2025</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR (R$) 2026</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR (R$) 2027</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>2024</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C2" t="s">
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>5011</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
-        </is>
+      <c r="E2" t="s">
+        <v>22</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -585,15 +697,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
-        </is>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
       </c>
       <c r="R2" t="n">
         <v>1000</v>
@@ -609,24 +717,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2024</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>5031</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
-        </is>
+      <c r="E3" t="s">
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
@@ -658,15 +762,11 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
-        </is>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
       </c>
       <c r="R3" t="n">
         <v>12580000</v>
@@ -682,24 +782,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2024</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>5071</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
-        </is>
+      <c r="E4" t="s">
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
@@ -731,15 +827,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
-        </is>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>29</v>
       </c>
       <c r="R4" t="n">
         <v>120000</v>
@@ -755,24 +847,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2024</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>5081</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E5" t="s">
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>17</v>
@@ -804,15 +892,11 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
       </c>
       <c r="R5" t="n">
         <v>50000000</v>
@@ -828,24 +912,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2024</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C6" t="s">
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>5081</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E6" t="s">
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
@@ -877,15 +957,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>50000000</v>
@@ -901,24 +977,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2024</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C7" t="s">
+        <v>21</v>
       </c>
       <c r="D7" t="n">
         <v>5081</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E7" t="s">
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>17</v>
@@ -950,15 +1022,11 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>33</v>
       </c>
       <c r="R7" t="n">
         <v>250000000</v>
@@ -974,24 +1042,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2024</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>5081</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E8" t="s">
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
@@ -1023,15 +1087,11 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
       </c>
       <c r="R8" t="n">
         <v>1062500000</v>
@@ -1047,24 +1107,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>2024</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C9" t="s">
+        <v>21</v>
       </c>
       <c r="D9" t="n">
         <v>5081</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E9" t="s">
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
@@ -1096,15 +1152,11 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>33</v>
       </c>
       <c r="R9" t="n">
         <v>40000000</v>
@@ -1120,24 +1172,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>2024</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>5081</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E10" t="s">
+        <v>30</v>
       </c>
       <c r="F10" t="n">
         <v>17</v>
@@ -1169,15 +1217,11 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>33</v>
       </c>
       <c r="R10" t="n">
         <v>100000000</v>
@@ -1193,24 +1237,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2024</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C11" t="s">
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>5081</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E11" t="s">
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
@@ -1242,15 +1282,11 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>33</v>
       </c>
       <c r="R11" t="n">
         <v>97500000</v>
@@ -1266,24 +1302,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2024</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C12" t="s">
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>5081</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="E12" t="s">
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
@@ -1315,15 +1347,11 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
-        </is>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>34</v>
       </c>
       <c r="R12" t="n">
         <v>45752420</v>
@@ -1339,24 +1367,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2024</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
       <c r="D13" t="n">
         <v>5121</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
+      <c r="E13" t="s">
+        <v>35</v>
       </c>
       <c r="F13" t="n">
         <v>25</v>
@@ -1388,15 +1412,11 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS CEMIG</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
-        </is>
+      <c r="P13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>37</v>
       </c>
       <c r="R13" t="n">
         <v>344720630</v>
@@ -1412,24 +1432,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2024</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C14" t="s">
+        <v>21</v>
       </c>
       <c r="D14" t="n">
         <v>5121</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
+      <c r="E14" t="s">
+        <v>35</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
@@ -1461,15 +1477,11 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS CEMIG</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
-        </is>
+      <c r="P14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>38</v>
       </c>
       <c r="R14" t="n">
         <v>40000</v>
@@ -1485,24 +1497,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2024</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C15" t="s">
+        <v>21</v>
       </c>
       <c r="D15" t="n">
         <v>5131</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
-        </is>
+      <c r="E15" t="s">
+        <v>39</v>
       </c>
       <c r="F15" t="n">
         <v>22</v>
@@ -1534,15 +1542,11 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
+      <c r="P15" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>41</v>
       </c>
       <c r="R15" t="n">
         <v>500000</v>
@@ -1558,24 +1562,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2024</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C16" t="s">
+        <v>21</v>
       </c>
       <c r="D16" t="n">
         <v>5131</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
-        </is>
+      <c r="E16" t="s">
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>22</v>
@@ -1607,15 +1607,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
+      <c r="P16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>41</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1631,24 +1627,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2024</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C17" t="s">
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>5191</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="E17" t="s">
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -1680,15 +1672,11 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
+      <c r="P17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>44</v>
       </c>
       <c r="R17" t="n">
         <v>670000</v>
@@ -1704,24 +1692,20 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2024</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C18" t="s">
+        <v>21</v>
       </c>
       <c r="D18" t="n">
         <v>5191</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="E18" t="s">
+        <v>42</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -1753,15 +1737,11 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>46</v>
       </c>
       <c r="R18" t="n">
         <v>1000</v>
@@ -1777,24 +1757,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2024</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C19" t="s">
+        <v>21</v>
       </c>
       <c r="D19" t="n">
         <v>5191</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="E19" t="s">
+        <v>42</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1826,15 +1802,11 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
+      <c r="P19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>46</v>
       </c>
       <c r="R19" t="n">
         <v>186000</v>
@@ -1850,24 +1822,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2024</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C20" t="s">
+        <v>21</v>
       </c>
       <c r="D20" t="n">
         <v>5191</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="E20" t="s">
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -1899,15 +1867,11 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
+      <c r="P20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>47</v>
       </c>
       <c r="R20" t="n">
         <v>1000</v>
@@ -1923,24 +1887,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>2024</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C21" t="s">
+        <v>21</v>
       </c>
       <c r="D21" t="n">
         <v>5201</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
+      <c r="E21" t="s">
+        <v>48</v>
       </c>
       <c r="F21" t="n">
         <v>23</v>
@@ -1972,15 +1932,11 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
-        </is>
+      <c r="P21" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>50</v>
       </c>
       <c r="R21" t="n">
         <v>23908160</v>
@@ -1996,24 +1952,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>2024</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C22" t="s">
+        <v>21</v>
       </c>
       <c r="D22" t="n">
         <v>5201</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
+      <c r="E22" t="s">
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>23</v>
@@ -2045,15 +1997,11 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
-        </is>
+      <c r="P22" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>51</v>
       </c>
       <c r="R22" t="n">
         <v>600000000</v>
@@ -2069,24 +2017,20 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>2024</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C23" t="s">
+        <v>21</v>
       </c>
       <c r="D23" t="n">
         <v>5251</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
-        </is>
+      <c r="E23" t="s">
+        <v>52</v>
       </c>
       <c r="F23" t="n">
         <v>25</v>
@@ -2118,15 +2062,11 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
-        </is>
+      <c r="P23" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>53</v>
       </c>
       <c r="R23" t="n">
         <v>409881263</v>
@@ -2142,24 +2082,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>2024</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C24" t="s">
+        <v>21</v>
       </c>
       <c r="D24" t="n">
         <v>5381</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="E24" t="s">
+        <v>54</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -2191,15 +2127,11 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
+      <c r="P24" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>56</v>
       </c>
       <c r="R24" t="n">
         <v>4300000</v>
@@ -2215,24 +2147,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>2024</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C25" t="s">
+        <v>21</v>
       </c>
       <c r="D25" t="n">
         <v>5381</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="E25" t="s">
+        <v>54</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -2264,15 +2192,11 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
+      <c r="P25" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>56</v>
       </c>
       <c r="R25" t="n">
         <v>200000</v>
@@ -2288,24 +2212,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>2024</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C26" t="s">
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>5381</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="E26" t="s">
+        <v>54</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2337,15 +2257,11 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
+      <c r="P26" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>56</v>
       </c>
       <c r="R26" t="n">
         <v>1000</v>
@@ -2361,24 +2277,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>2024</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C27" t="s">
+        <v>21</v>
       </c>
       <c r="D27" t="n">
         <v>5381</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="E27" t="s">
+        <v>54</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -2410,15 +2322,11 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
+      <c r="P27" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>56</v>
       </c>
       <c r="R27" t="n">
         <v>4000000</v>
@@ -2434,24 +2342,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>2024</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C28" t="s">
+        <v>21</v>
       </c>
       <c r="D28" t="n">
         <v>5391</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E28" t="s">
+        <v>57</v>
       </c>
       <c r="F28" t="n">
         <v>25</v>
@@ -2483,15 +2387,11 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
-        </is>
+      <c r="P28" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>59</v>
       </c>
       <c r="R28" t="n">
         <v>198940203</v>
@@ -2507,24 +2407,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>2024</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C29" t="s">
+        <v>21</v>
       </c>
       <c r="D29" t="n">
         <v>5391</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E29" t="s">
+        <v>57</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
@@ -2556,15 +2452,11 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
-        </is>
+      <c r="P29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>60</v>
       </c>
       <c r="R29" t="n">
         <v>241821909</v>
@@ -2580,24 +2472,20 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>2024</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C30" t="s">
+        <v>21</v>
       </c>
       <c r="D30" t="n">
         <v>5391</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E30" t="s">
+        <v>57</v>
       </c>
       <c r="F30" t="n">
         <v>25</v>
@@ -2629,15 +2517,11 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
-        </is>
+      <c r="P30" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>61</v>
       </c>
       <c r="R30" t="n">
         <v>30805275</v>
@@ -2653,24 +2537,20 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>2024</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C31" t="s">
+        <v>21</v>
       </c>
       <c r="D31" t="n">
         <v>5391</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E31" t="s">
+        <v>57</v>
       </c>
       <c r="F31" t="n">
         <v>25</v>
@@ -2702,15 +2582,11 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
-        </is>
+      <c r="P31" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>63</v>
       </c>
       <c r="R31" t="n">
         <v>49096963</v>
@@ -2726,24 +2602,20 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>2024</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C32" t="s">
+        <v>21</v>
       </c>
       <c r="D32" t="n">
         <v>5391</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E32" t="s">
+        <v>57</v>
       </c>
       <c r="F32" t="n">
         <v>25</v>
@@ -2775,15 +2647,11 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
-        </is>
+      <c r="P32" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>64</v>
       </c>
       <c r="R32" t="n">
         <v>130600000</v>
@@ -2799,24 +2667,20 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>2024</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C33" t="s">
+        <v>21</v>
       </c>
       <c r="D33" t="n">
         <v>5391</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E33" t="s">
+        <v>57</v>
       </c>
       <c r="F33" t="n">
         <v>25</v>
@@ -2848,15 +2712,11 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
-        </is>
+      <c r="P33" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>65</v>
       </c>
       <c r="R33" t="n">
         <v>13194360</v>
@@ -2872,24 +2732,20 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>2024</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C34" t="s">
+        <v>21</v>
       </c>
       <c r="D34" t="n">
         <v>5391</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="E34" t="s">
+        <v>57</v>
       </c>
       <c r="F34" t="n">
         <v>25</v>
@@ -2921,15 +2777,11 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="P34" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>66</v>
       </c>
       <c r="R34" t="n">
         <v>508846661</v>
@@ -2945,24 +2797,20 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>2024</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C35" t="s">
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>5401</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
+      <c r="E35" t="s">
+        <v>67</v>
       </c>
       <c r="F35" t="n">
         <v>25</v>
@@ -2994,15 +2842,11 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
-        </is>
+      <c r="P35" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>69</v>
       </c>
       <c r="R35" t="n">
         <v>3487433034</v>
@@ -3018,24 +2862,20 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>2024</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C36" t="s">
+        <v>21</v>
       </c>
       <c r="D36" t="n">
         <v>5401</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
+      <c r="E36" t="s">
+        <v>67</v>
       </c>
       <c r="F36" t="n">
         <v>25</v>
@@ -3067,15 +2907,11 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
-        </is>
+      <c r="P36" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>70</v>
       </c>
       <c r="R36" t="n">
         <v>247223810</v>
@@ -3091,24 +2927,20 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>2024</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C37" t="s">
+        <v>21</v>
       </c>
       <c r="D37" t="n">
         <v>5511</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
+      <c r="E37" t="s">
+        <v>71</v>
       </c>
       <c r="F37" t="n">
         <v>17</v>
@@ -3140,15 +2972,11 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
-        </is>
+      <c r="P37" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>72</v>
       </c>
       <c r="R37" t="n">
         <v>2000000</v>
@@ -3164,24 +2992,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>2024</v>
       </c>
       <c r="B38" t="n">
         <v>1220</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C38" t="s">
+        <v>21</v>
       </c>
       <c r="D38" t="n">
         <v>5511</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
+      <c r="E38" t="s">
+        <v>71</v>
       </c>
       <c r="F38" t="n">
         <v>17</v>
@@ -3213,15 +3037,11 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
+      <c r="P38" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>73</v>
       </c>
       <c r="R38" t="n">
         <v>45000000</v>
@@ -3237,24 +3057,20 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>2024</v>
       </c>
       <c r="B39" t="n">
         <v>1300</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
-        </is>
+      <c r="C39" t="s">
+        <v>74</v>
       </c>
       <c r="D39" t="n">
         <v>5261</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
-        </is>
+      <c r="E39" t="s">
+        <v>75</v>
       </c>
       <c r="F39" t="n">
         <v>26</v>
@@ -3286,15 +3102,11 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
-        </is>
+      <c r="P39" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>76</v>
       </c>
       <c r="R39" t="n">
         <v>1000</v>
@@ -3310,24 +3122,20 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>2024</v>
       </c>
       <c r="B40" t="n">
         <v>1500</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
+      <c r="C40" t="s">
+        <v>77</v>
       </c>
       <c r="D40" t="n">
         <v>5141</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
+      <c r="E40" t="s">
+        <v>78</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -3359,15 +3167,11 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
-        </is>
+      <c r="P40" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>3280000</v>
@@ -3383,24 +3187,20 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>2024</v>
       </c>
       <c r="B41" t="n">
         <v>1500</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
+      <c r="C41" t="s">
+        <v>77</v>
       </c>
       <c r="D41" t="n">
         <v>5141</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
+      <c r="E41" t="s">
+        <v>78</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -3432,15 +3232,11 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
+      <c r="P41" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>81</v>
       </c>
       <c r="R41" t="n">
         <v>35386354</v>
@@ -3456,6 +3252,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -503,43 +503,43 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2023</t>
+          <t>VALOR (R$) 2024</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2024</t>
+          <t>VALOR (R$) 2025</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2025</t>
+          <t>VALOR (R$) 2026</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2026</t>
+          <t>VALOR (R$) 2027</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5191</v>
+        <v>5011</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -549,22 +549,22 @@
         <v>122</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>6011</v>
+        <v>3017</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N2" t="n">
         <v>51000</v>
@@ -574,70 +574,70 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>90000</v>
+        <v>1000</v>
       </c>
       <c r="S2" t="n">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="n">
-        <v>50000</v>
+        <v>1000</v>
       </c>
       <c r="U2" t="n">
-        <v>50000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5191</v>
+        <v>5031</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>6003</v>
+        <v>3015</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N3" t="n">
         <v>51000</v>
@@ -647,16 +647,16 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL, À CAPTAÇÃO E À COORDENAÇÃO DA TRANSFERÊNCIA DE RECURSOS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>15882556</v>
+        <v>12580000</v>
       </c>
       <c r="S3" t="n">
         <v>1000</v>
@@ -670,153 +670,153 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5191</v>
+        <v>5071</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>705</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>6001</v>
+        <v>6010</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N4" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="T4" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="U4" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5191</v>
+        <v>5081</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>512</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>6001</v>
+        <v>6009</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N5" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="T5" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -827,36 +827,36 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5011</v>
+        <v>5081</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="H6" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>3014</v>
+        <v>6009</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N6" t="n">
         <v>51000</v>
@@ -866,30 +866,30 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MINAS + GERAIS - DIVERSIFICAÇÃO E FORTALECIMENTO DA ECONOMIA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="T6" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="U6" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -900,69 +900,69 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5031</v>
+        <v>5081</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>572</v>
+        <v>512</v>
       </c>
       <c r="H7" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>3017</v>
+        <v>8008</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N7" t="n">
-        <v>51000</v>
+        <v>21204</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MINAS + GERAIS - DIVERSIFICAÇÃO E FORTALECIMENTO DA ECONOMIA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>GESTÃO DE PARTICIPAÇÕES, FUNDOS, CONSÓRCIOS, P&amp;D E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>14119841</v>
+        <v>250000000</v>
       </c>
       <c r="S7" t="n">
-        <v>3737589</v>
+        <v>250000000</v>
       </c>
       <c r="T7" t="n">
-        <v>3737589</v>
+        <v>250000000</v>
       </c>
       <c r="U7" t="n">
-        <v>3737589</v>
+        <v>250000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -987,16 +987,16 @@
         <v>512</v>
       </c>
       <c r="H8" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I8" t="n">
         <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1005,14 +1005,14 @@
         <v>4610</v>
       </c>
       <c r="N8" t="n">
-        <v>21204</v>
+        <v>22199</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>250000000</v>
+        <v>1062500000</v>
       </c>
       <c r="S8" t="n">
-        <v>250000000</v>
+        <v>1040500000</v>
       </c>
       <c r="T8" t="n">
-        <v>250000000</v>
+        <v>1040500000</v>
       </c>
       <c r="U8" t="n">
-        <v>250000000</v>
+        <v>1040500000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1060,16 +1060,16 @@
         <v>512</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>885250000</v>
+        <v>40000000</v>
       </c>
       <c r="S9" t="n">
-        <v>1055250000</v>
+        <v>40000000</v>
       </c>
       <c r="T9" t="n">
-        <v>1055250000</v>
+        <v>40000000</v>
       </c>
       <c r="U9" t="n">
-        <v>1055250000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1133,16 +1133,16 @@
         <v>512</v>
       </c>
       <c r="H10" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
         <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1151,14 +1151,14 @@
         <v>4610</v>
       </c>
       <c r="N10" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="T10" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="U10" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1206,16 +1206,16 @@
         <v>512</v>
       </c>
       <c r="H11" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>80000000</v>
+        <v>97500000</v>
       </c>
       <c r="S11" t="n">
-        <v>80000000</v>
+        <v>97500000</v>
       </c>
       <c r="T11" t="n">
-        <v>80000000</v>
+        <v>97500000</v>
       </c>
       <c r="U11" t="n">
-        <v>80000000</v>
+        <v>97500000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1279,16 +1279,16 @@
         <v>512</v>
       </c>
       <c r="H12" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>8004</v>
+        <v>8009</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1304,30 +1304,30 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>74750000</v>
+        <v>45752420</v>
       </c>
       <c r="S12" t="n">
-        <v>74750000</v>
+        <v>42380044</v>
       </c>
       <c r="T12" t="n">
-        <v>74750000</v>
+        <v>42380044</v>
       </c>
       <c r="U12" t="n">
-        <v>74750000</v>
+        <v>42380044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1338,36 +1338,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H13" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>8005</v>
+        <v>3010</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N13" t="n">
         <v>51000</v>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPP - SISTEMA ADUTOR RIO MANSO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>49915500</v>
+        <v>344720630</v>
       </c>
       <c r="S13" t="n">
-        <v>55500000</v>
+        <v>222303420</v>
       </c>
       <c r="T13" t="n">
-        <v>55500000</v>
+        <v>4942214</v>
       </c>
       <c r="U13" t="n">
-        <v>55500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1411,69 +1411,69 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>8008</v>
+        <v>3011</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N14" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>31000000</v>
+        <v>40000</v>
       </c>
       <c r="S14" t="n">
-        <v>31000000</v>
+        <v>40000</v>
       </c>
       <c r="T14" t="n">
-        <v>31000000</v>
+        <v>40000</v>
       </c>
       <c r="U14" t="n">
-        <v>31000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1484,30 +1484,30 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5081</v>
+        <v>5131</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>8008</v>
+        <v>6008</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1523,30 +1523,30 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>50000000</v>
+        <v>500000</v>
       </c>
       <c r="S15" t="n">
-        <v>50000000</v>
+        <v>500000</v>
       </c>
       <c r="T15" t="n">
-        <v>50000000</v>
+        <v>500000</v>
       </c>
       <c r="U15" t="n">
-        <v>50000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1557,36 +1557,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5121</v>
+        <v>5131</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H16" t="n">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>3011</v>
+        <v>6008</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N16" t="n">
         <v>51000</v>
@@ -1596,16 +1596,16 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>30608</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1614,12 +1614,12 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1630,69 +1630,69 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5121</v>
+        <v>5191</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>3012</v>
+        <v>6011</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N17" t="n">
-        <v>12100</v>
+        <v>51000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>629198369</v>
+        <v>670000</v>
       </c>
       <c r="S17" t="n">
-        <v>178381605</v>
+        <v>150000</v>
       </c>
       <c r="T17" t="n">
-        <v>194067776</v>
+        <v>110000</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1703,69 +1703,69 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5131</v>
+        <v>5191</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO INTEGRADO DE MINAS GERAIS - INDI</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>6008</v>
+        <v>6002</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N18" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO INDI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>500000</v>
+        <v>1000</v>
       </c>
       <c r="S18" t="n">
-        <v>500000</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="n">
-        <v>500000</v>
+        <v>1000</v>
       </c>
       <c r="U18" t="n">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -1776,30 +1776,30 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>122</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1808,37 +1808,37 @@
         <v>4810</v>
       </c>
       <c r="N19" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>21267000</v>
+        <v>186000</v>
       </c>
       <c r="S19" t="n">
-        <v>21267000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="n">
-        <v>21267000</v>
+        <v>1000</v>
       </c>
       <c r="U19" t="n">
-        <v>21267000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -1849,69 +1849,69 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5251</v>
+        <v>5191</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>451</v>
+        <v>123</v>
       </c>
       <c r="H20" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>8003</v>
+        <v>6001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N20" t="n">
-        <v>12900</v>
+        <v>51000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>#VEMPRAMINAS - ATRAÇÃO DE INVESTIMENTOS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>244358023</v>
+        <v>1000</v>
       </c>
       <c r="S20" t="n">
-        <v>504956974</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="n">
-        <v>624697390</v>
+        <v>1000</v>
       </c>
       <c r="U20" t="n">
-        <v>229815496</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -1922,69 +1922,69 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5391</v>
+        <v>5201</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>3004</v>
+        <v>6004</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N21" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>308709015</v>
+        <v>23908160</v>
       </c>
       <c r="S21" t="n">
-        <v>163064280</v>
+        <v>23908000</v>
       </c>
       <c r="T21" t="n">
-        <v>79596239</v>
+        <v>23908000</v>
       </c>
       <c r="U21" t="n">
-        <v>586579</v>
+        <v>23908000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -1995,69 +1995,69 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5391</v>
+        <v>5201</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>752</v>
+        <v>694</v>
       </c>
       <c r="H22" t="n">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>3005</v>
+        <v>8006</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N22" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>120452442</v>
+        <v>600000000</v>
       </c>
       <c r="S22" t="n">
-        <v>250718817</v>
+        <v>400000000</v>
       </c>
       <c r="T22" t="n">
-        <v>242972752</v>
+        <v>1000</v>
       </c>
       <c r="U22" t="n">
-        <v>330665231</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2068,69 +2068,69 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="H23" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>3006</v>
+        <v>3018</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4610</v>
+        <v>4899</v>
       </c>
       <c r="N23" t="n">
-        <v>51000</v>
+        <v>61000</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4693805</v>
+        <v>409881263</v>
       </c>
       <c r="S23" t="n">
-        <v>3535135</v>
+        <v>416795211</v>
       </c>
       <c r="T23" t="n">
-        <v>3602141</v>
+        <v>433214634</v>
       </c>
       <c r="U23" t="n">
-        <v>6764431</v>
+        <v>285354938</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2141,30 +2141,30 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3001</v>
+        <v>8002</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2180,30 +2180,30 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1880000000</v>
+        <v>4300000</v>
       </c>
       <c r="S24" t="n">
-        <v>2020000000</v>
+        <v>4000000</v>
       </c>
       <c r="T24" t="n">
-        <v>3270000000</v>
+        <v>3500000</v>
       </c>
       <c r="U24" t="n">
-        <v>3400000000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2214,30 +2214,30 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>3007</v>
+        <v>8002</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2253,30 +2253,30 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>17888000</v>
+        <v>200000</v>
       </c>
       <c r="S25" t="n">
-        <v>3202147</v>
+        <v>200000</v>
       </c>
       <c r="T25" t="n">
-        <v>7501423</v>
+        <v>200000</v>
       </c>
       <c r="U25" t="n">
-        <v>13788616</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2287,69 +2287,69 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H26" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>3008</v>
+        <v>8002</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N26" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>15165514</v>
+        <v>1000</v>
       </c>
       <c r="S26" t="n">
-        <v>2596418</v>
+        <v>1000</v>
       </c>
       <c r="T26" t="n">
-        <v>2773623</v>
+        <v>1000</v>
       </c>
       <c r="U26" t="n">
-        <v>9733481</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2360,69 +2360,69 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H27" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>3009</v>
+        <v>8002</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N27" t="n">
-        <v>12100</v>
+        <v>51000</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>12241405</v>
+        <v>4000000</v>
       </c>
       <c r="S27" t="n">
-        <v>10327800</v>
+        <v>2500000</v>
       </c>
       <c r="T27" t="n">
-        <v>10651410</v>
+        <v>2000000</v>
       </c>
       <c r="U27" t="n">
-        <v>11290495</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2433,11 +2433,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2447,16 +2447,16 @@
         <v>752</v>
       </c>
       <c r="H28" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I28" t="n">
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2472,30 +2472,30 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>2901796000</v>
+        <v>198940203</v>
       </c>
       <c r="S28" t="n">
-        <v>3487433000</v>
+        <v>224669708</v>
       </c>
       <c r="T28" t="n">
-        <v>3930724000</v>
+        <v>92100648</v>
       </c>
       <c r="U28" t="n">
-        <v>4329559000</v>
+        <v>13570642</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2506,11 +2506,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2520,16 +2520,16 @@
         <v>752</v>
       </c>
       <c r="H29" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I29" t="n">
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>3003</v>
+        <v>3005</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2545,30 +2545,30 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>162092993</v>
+        <v>241821909</v>
       </c>
       <c r="S29" t="n">
-        <v>74451231</v>
+        <v>515862966</v>
       </c>
       <c r="T29" t="n">
-        <v>75686208</v>
+        <v>537405240</v>
       </c>
       <c r="U29" t="n">
-        <v>104538653</v>
+        <v>480353203</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2579,30 +2579,30 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H30" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>8006</v>
+        <v>3006</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2618,30 +2618,30 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>45000000</v>
+        <v>30805275</v>
       </c>
       <c r="S30" t="n">
-        <v>45000000</v>
+        <v>15389442</v>
       </c>
       <c r="T30" t="n">
-        <v>45000000</v>
+        <v>4894000</v>
       </c>
       <c r="U30" t="n">
-        <v>45000000</v>
+        <v>25171936</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -2652,30 +2652,30 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G31" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H31" t="n">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>8007</v>
+        <v>3001</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2691,137 +2691,137 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>2000000</v>
+        <v>49096963</v>
       </c>
       <c r="S31" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5261</v>
+        <v>5391</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="H32" t="n">
-        <v>705</v>
+        <v>94</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>8011</v>
+        <v>3007</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N32" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>1000</v>
+        <v>130600000</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>174928000</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>139546000</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>125024000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="n">
-        <v>1480</v>
+        <v>1220</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5071</v>
+        <v>5391</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H33" t="n">
-        <v>705</v>
+        <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>6010</v>
+        <v>3008</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2837,70 +2837,70 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>120000</v>
+        <v>13194360</v>
       </c>
       <c r="S33" t="n">
-        <v>120000</v>
+        <v>8683890</v>
       </c>
       <c r="T33" t="n">
-        <v>120000</v>
+        <v>13879558</v>
       </c>
       <c r="U33" t="n">
-        <v>120000</v>
+        <v>70075101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5141</v>
+        <v>5391</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G34" t="n">
-        <v>126</v>
+        <v>752</v>
       </c>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>8001</v>
+        <v>3014</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N34" t="n">
         <v>51000</v>
@@ -2910,64 +2910,64 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>45914908</v>
+        <v>508846661</v>
       </c>
       <c r="S34" t="n">
-        <v>6210000</v>
+        <v>2115585319</v>
       </c>
       <c r="T34" t="n">
-        <v>6210000</v>
+        <v>511690078</v>
       </c>
       <c r="U34" t="n">
-        <v>6210000</v>
+        <v>119701000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5381</v>
+        <v>5401</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H35" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>8002</v>
+        <v>3002</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2983,64 +2983,64 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>3300000</v>
+        <v>3487433034</v>
       </c>
       <c r="S35" t="n">
-        <v>3300000</v>
+        <v>3930724350</v>
       </c>
       <c r="T35" t="n">
-        <v>2800000</v>
+        <v>4329558721</v>
       </c>
       <c r="U35" t="n">
-        <v>2800000</v>
+        <v>3703598493</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5381</v>
+        <v>5401</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H36" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>8002</v>
+        <v>3003</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3056,143 +3056,143 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>200000</v>
+        <v>247223810</v>
       </c>
       <c r="S36" t="n">
-        <v>200000</v>
+        <v>224139298</v>
       </c>
       <c r="T36" t="n">
-        <v>200000</v>
+        <v>143327686</v>
       </c>
       <c r="U36" t="n">
-        <v>200000</v>
+        <v>188131849</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5381</v>
+        <v>5511</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G37" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="H37" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>8002</v>
+        <v>6012</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N37" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="S37" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="T37" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="U37" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5381</v>
+        <v>5511</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G38" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="H38" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I38" t="n">
         <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>8002</v>
+        <v>8012</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N38" t="n">
         <v>51000</v>
@@ -3202,25 +3202,244 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4500000</v>
+        <v>45000000</v>
       </c>
       <c r="S38" t="n">
-        <v>2500000</v>
+        <v>45000000</v>
       </c>
       <c r="T38" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
       <c r="U38" t="n">
-        <v>1000000</v>
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5261</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>26</v>
+      </c>
+      <c r="G39" t="n">
+        <v>783</v>
+      </c>
+      <c r="H39" t="n">
+        <v>705</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8011</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4510</v>
+      </c>
+      <c r="N39" t="n">
+        <v>11101</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>126</v>
+      </c>
+      <c r="H40" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6006</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N40" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>13250000</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>126</v>
+      </c>
+      <c r="H41" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8001</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4810</v>
+      </c>
+      <c r="N41" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>35386354</v>
+      </c>
+      <c r="S41" t="n">
+        <v>39030861</v>
+      </c>
+      <c r="T41" t="n">
+        <v>31646705</v>
+      </c>
+      <c r="U41" t="n">
+        <v>26305815</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1062500000</v>
+        <v>40000000</v>
       </c>
       <c r="S8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="T8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="U8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="9">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>40000000</v>
+        <v>1062500000</v>
       </c>
       <c r="S9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="T9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="U9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
     </row>
     <row r="10">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="S10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="T10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="U10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="S11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="T11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="U11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2189,16 +2189,16 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4300000</v>
+        <v>200000</v>
       </c>
       <c r="S24" t="n">
-        <v>4000000</v>
+        <v>200000</v>
       </c>
       <c r="T24" t="n">
-        <v>3500000</v>
+        <v>200000</v>
       </c>
       <c r="U24" t="n">
-        <v>3500000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="25">
@@ -2262,16 +2262,16 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>200000</v>
+        <v>4300000</v>
       </c>
       <c r="S25" t="n">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="T25" t="n">
-        <v>200000</v>
+        <v>3500000</v>
       </c>
       <c r="U25" t="n">
-        <v>200000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="26">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="S10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="T10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="U10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="S11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="T11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="U11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
     </row>
     <row r="12">
@@ -1557,30 +1557,30 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5131</v>
+        <v>5191</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>122</v>
       </c>
       <c r="H16" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1596,25 +1596,25 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>670000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="17">
@@ -1644,16 +1644,16 @@
         <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>6011</v>
+        <v>6002</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1662,32 +1662,32 @@
         <v>4810</v>
       </c>
       <c r="N17" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>670000</v>
+        <v>1000</v>
       </c>
       <c r="S17" t="n">
-        <v>150000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="n">
-        <v>110000</v>
+        <v>1000</v>
       </c>
       <c r="U17" t="n">
-        <v>90000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -1735,7 +1735,7 @@
         <v>4810</v>
       </c>
       <c r="N18" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1000</v>
+        <v>186000</v>
       </c>
       <c r="S18" t="n">
         <v>1000</v>
@@ -1787,25 +1787,25 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N19" t="n">
         <v>51000</v>
@@ -1815,16 +1815,16 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>186000</v>
+        <v>1000</v>
       </c>
       <c r="S19" t="n">
         <v>1000</v>
@@ -1849,64 +1849,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5191</v>
+        <v>5201</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N20" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1000</v>
+        <v>23908160</v>
       </c>
       <c r="S20" t="n">
-        <v>1000</v>
+        <v>23908000</v>
       </c>
       <c r="T20" t="n">
-        <v>1000</v>
+        <v>23908000</v>
       </c>
       <c r="U20" t="n">
-        <v>1000</v>
+        <v>23908000</v>
       </c>
     </row>
     <row r="21">
@@ -1933,19 +1933,19 @@
         <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
         <v>6</v>
       </c>
-      <c r="J21" t="n">
-        <v>4</v>
-      </c>
       <c r="K21" t="n">
-        <v>6004</v>
+        <v>8006</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1961,25 +1961,25 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>23908160</v>
+        <v>600000000</v>
       </c>
       <c r="S21" t="n">
-        <v>23908000</v>
+        <v>400000000</v>
       </c>
       <c r="T21" t="n">
-        <v>23908000</v>
+        <v>1000</v>
       </c>
       <c r="U21" t="n">
-        <v>23908000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
@@ -1995,64 +1995,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5201</v>
+        <v>5251</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>694</v>
+        <v>121</v>
       </c>
       <c r="H22" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>8006</v>
+        <v>3018</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4810</v>
+        <v>4899</v>
       </c>
       <c r="N22" t="n">
-        <v>12400</v>
+        <v>61000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>600000000</v>
+        <v>409881263</v>
       </c>
       <c r="S22" t="n">
-        <v>400000000</v>
+        <v>416795211</v>
       </c>
       <c r="T22" t="n">
-        <v>1000</v>
+        <v>433214634</v>
       </c>
       <c r="U22" t="n">
-        <v>1000</v>
+        <v>285354938</v>
       </c>
     </row>
     <row r="23">
@@ -2068,64 +2068,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5251</v>
+        <v>5381</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H23" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>3018</v>
+        <v>8002</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4899</v>
+        <v>4610</v>
       </c>
       <c r="N23" t="n">
-        <v>61000</v>
+        <v>51000</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>409881263</v>
+        <v>4300000</v>
       </c>
       <c r="S23" t="n">
-        <v>416795211</v>
+        <v>4000000</v>
       </c>
       <c r="T23" t="n">
-        <v>433214634</v>
+        <v>3500000</v>
       </c>
       <c r="U23" t="n">
-        <v>285354938</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="24">
@@ -2243,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N25" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2262,16 +2262,16 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4300000</v>
+        <v>1000</v>
       </c>
       <c r="S25" t="n">
-        <v>4000000</v>
+        <v>1000</v>
       </c>
       <c r="T25" t="n">
-        <v>3500000</v>
+        <v>1000</v>
       </c>
       <c r="U25" t="n">
-        <v>3500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -2319,7 +2319,7 @@
         <v>4810</v>
       </c>
       <c r="N26" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>1000</v>
+        <v>4000000</v>
       </c>
       <c r="S26" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="T26" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="U26" t="n">
-        <v>1000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="27">
@@ -2360,36 +2360,36 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>752</v>
+      </c>
+      <c r="H27" t="n">
+        <v>92</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
         <v>4</v>
       </c>
-      <c r="G27" t="n">
-        <v>122</v>
-      </c>
-      <c r="H27" t="n">
-        <v>57</v>
-      </c>
-      <c r="I27" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
       <c r="K27" t="n">
-        <v>8002</v>
+        <v>3004</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N27" t="n">
         <v>51000</v>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4000000</v>
+        <v>198940203</v>
       </c>
       <c r="S27" t="n">
-        <v>2500000</v>
+        <v>224669708</v>
       </c>
       <c r="T27" t="n">
-        <v>2000000</v>
+        <v>92100648</v>
       </c>
       <c r="U27" t="n">
-        <v>1500000</v>
+        <v>13570642</v>
       </c>
     </row>
     <row r="28">
@@ -2453,10 +2453,10 @@
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>198940203</v>
+        <v>241821909</v>
       </c>
       <c r="S28" t="n">
-        <v>224669708</v>
+        <v>515862966</v>
       </c>
       <c r="T28" t="n">
-        <v>92100648</v>
+        <v>537405240</v>
       </c>
       <c r="U28" t="n">
-        <v>13570642</v>
+        <v>480353203</v>
       </c>
     </row>
     <row r="29">
@@ -2526,10 +2526,10 @@
         <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2550,20 +2550,20 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>241821909</v>
+        <v>30805275</v>
       </c>
       <c r="S29" t="n">
-        <v>515862966</v>
+        <v>15389442</v>
       </c>
       <c r="T29" t="n">
-        <v>537405240</v>
+        <v>4894000</v>
       </c>
       <c r="U29" t="n">
-        <v>480353203</v>
+        <v>25171936</v>
       </c>
     </row>
     <row r="30">
@@ -2593,16 +2593,16 @@
         <v>752</v>
       </c>
       <c r="H30" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3006</v>
+        <v>3001</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2618,25 +2618,25 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>30805275</v>
+        <v>49096963</v>
       </c>
       <c r="S30" t="n">
-        <v>15389442</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4894000</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>25171936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2672,10 +2672,10 @@
         <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2696,20 +2696,20 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>49096963</v>
+        <v>130600000</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>174928000</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>139546000</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>125024000</v>
       </c>
     </row>
     <row r="32">
@@ -2745,10 +2745,10 @@
         <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2769,20 +2769,20 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>130600000</v>
+        <v>13194360</v>
       </c>
       <c r="S32" t="n">
-        <v>174928000</v>
+        <v>8683890</v>
       </c>
       <c r="T32" t="n">
-        <v>139546000</v>
+        <v>13879558</v>
       </c>
       <c r="U32" t="n">
-        <v>125024000</v>
+        <v>70075101</v>
       </c>
     </row>
     <row r="33">
@@ -2818,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>3008</v>
+        <v>3014</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N33" t="n">
         <v>51000</v>
@@ -2842,20 +2842,20 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>13194360</v>
+        <v>508846661</v>
       </c>
       <c r="S33" t="n">
-        <v>8683890</v>
+        <v>2115585319</v>
       </c>
       <c r="T33" t="n">
-        <v>13879558</v>
+        <v>511690078</v>
       </c>
       <c r="U33" t="n">
-        <v>70075101</v>
+        <v>119701000</v>
       </c>
     </row>
     <row r="34">
@@ -2871,11 +2871,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5391</v>
+        <v>5401</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2885,22 +2885,22 @@
         <v>752</v>
       </c>
       <c r="H34" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3014</v>
+        <v>3002</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N34" t="n">
         <v>51000</v>
@@ -2910,25 +2910,25 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>508846661</v>
+        <v>3487433034</v>
       </c>
       <c r="S34" t="n">
-        <v>2115585319</v>
+        <v>3930724350</v>
       </c>
       <c r="T34" t="n">
-        <v>511690078</v>
+        <v>4329558721</v>
       </c>
       <c r="U34" t="n">
-        <v>119701000</v>
+        <v>3703598493</v>
       </c>
     </row>
     <row r="35">
@@ -2964,10 +2964,10 @@
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2988,20 +2988,20 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>3487433034</v>
+        <v>247223810</v>
       </c>
       <c r="S35" t="n">
-        <v>3930724350</v>
+        <v>224139298</v>
       </c>
       <c r="T35" t="n">
-        <v>4329558721</v>
+        <v>143327686</v>
       </c>
       <c r="U35" t="n">
-        <v>3703598493</v>
+        <v>188131849</v>
       </c>
     </row>
     <row r="36">
@@ -3017,30 +3017,30 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5401</v>
+        <v>5511</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G36" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="H36" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>3003</v>
+        <v>6012</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3056,25 +3056,25 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>247223810</v>
+        <v>2000000</v>
       </c>
       <c r="S36" t="n">
-        <v>224139298</v>
+        <v>2000000</v>
       </c>
       <c r="T36" t="n">
-        <v>143327686</v>
+        <v>2000000</v>
       </c>
       <c r="U36" t="n">
-        <v>188131849</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="37">
@@ -3107,13 +3107,13 @@
         <v>21</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
         <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>6012</v>
+        <v>8012</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
       <c r="S37" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
       <c r="T37" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
       <c r="U37" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="38">
@@ -3155,72 +3155,72 @@
         <v>2024</v>
       </c>
       <c r="B38" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5511</v>
+        <v>5261</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>512</v>
+        <v>783</v>
       </c>
       <c r="H38" t="n">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="I38" t="n">
         <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N38" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>45000000</v>
+        <v>1000</v>
       </c>
       <c r="S38" t="n">
-        <v>45000000</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>45000000</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>45000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3228,72 +3228,72 @@
         <v>2024</v>
       </c>
       <c r="B39" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5261</v>
+        <v>5141</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>783</v>
+        <v>126</v>
       </c>
       <c r="H39" t="n">
-        <v>705</v>
+        <v>30</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>8011</v>
+        <v>6006</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N39" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>1000</v>
+        <v>3280000</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>13250000</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>6250000</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3250000</v>
       </c>
     </row>
     <row r="40">
@@ -3326,19 +3326,19 @@
         <v>30</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>6006</v>
+        <v>8001</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N40" t="n">
         <v>51000</v>
@@ -3353,92 +3353,19 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>3280000</v>
+        <v>35386354</v>
       </c>
       <c r="S40" t="n">
-        <v>13250000</v>
+        <v>39030861</v>
       </c>
       <c r="T40" t="n">
-        <v>6250000</v>
+        <v>31646705</v>
       </c>
       <c r="U40" t="n">
-        <v>3250000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>5141</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>4</v>
-      </c>
-      <c r="G41" t="n">
-        <v>126</v>
-      </c>
-      <c r="H41" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>8001</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4810</v>
-      </c>
-      <c r="N41" t="n">
-        <v>51000</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
-        <v>35386354</v>
-      </c>
-      <c r="S41" t="n">
-        <v>39030861</v>
-      </c>
-      <c r="T41" t="n">
-        <v>31646705</v>
-      </c>
-      <c r="U41" t="n">
         <v>26305815</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>40000000</v>
+        <v>1062500000</v>
       </c>
       <c r="S8" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="T8" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="U8" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
     </row>
     <row r="9">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1062500000</v>
+        <v>40000000</v>
       </c>
       <c r="S9" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="T9" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="U9" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="10">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="S10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="T10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="U10" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="S11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="T11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="U11" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12">
@@ -3214,13 +3214,13 @@
         <v>1000</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="39">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1062500000</v>
+        <v>40000000</v>
       </c>
       <c r="S8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="T8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
       <c r="U8" t="n">
-        <v>1040500000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="9">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>40000000</v>
+        <v>1062500000</v>
       </c>
       <c r="S9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="T9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
       <c r="U9" t="n">
-        <v>40000000</v>
+        <v>1040500000</v>
       </c>
     </row>
     <row r="10">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="S10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="T10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
       <c r="U10" t="n">
-        <v>97500000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="S11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="T11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
       <c r="U11" t="n">
-        <v>100000000</v>
+        <v>97500000</v>
       </c>
     </row>
     <row r="12">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -503,28 +503,28 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2024</t>
+          <t>VALOR (R$) 2025</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2025</t>
+          <t>VALOR (R$) 2026</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2026</t>
+          <t>VALOR (R$) 2027</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2027</t>
+          <t>VALOR (R$) 2028</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -612,7 +612,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -656,21 +656,21 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>12580000</v>
+        <v>6380000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -681,30 +681,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5071</v>
+        <v>5031</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="H4" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>6010</v>
+        <v>3015</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -720,30 +720,30 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>120000</v>
+        <v>6240000</v>
       </c>
       <c r="S4" t="n">
-        <v>120000</v>
+        <v>1000000</v>
       </c>
       <c r="T4" t="n">
-        <v>120000</v>
+        <v>1000000</v>
       </c>
       <c r="U4" t="n">
-        <v>120000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -754,30 +754,30 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5081</v>
+        <v>5071</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -786,37 +786,37 @@
         <v>4610</v>
       </c>
       <c r="N5" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>50000000</v>
+        <v>120000</v>
       </c>
       <c r="S5" t="n">
-        <v>50000000</v>
+        <v>120000</v>
       </c>
       <c r="T5" t="n">
-        <v>50000000</v>
+        <v>120000</v>
       </c>
       <c r="U5" t="n">
-        <v>50000000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -859,7 +859,7 @@
         <v>4610</v>
       </c>
       <c r="N6" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -917,13 +917,13 @@
         <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>8008</v>
+        <v>6009</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>4610</v>
       </c>
       <c r="N7" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -944,25 +944,25 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>250000000</v>
+        <v>50000000</v>
       </c>
       <c r="S7" t="n">
-        <v>250000000</v>
+        <v>50000000</v>
       </c>
       <c r="T7" t="n">
-        <v>250000000</v>
+        <v>50000000</v>
       </c>
       <c r="U7" t="n">
-        <v>250000000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -1005,7 +1005,7 @@
         <v>4610</v>
       </c>
       <c r="N8" t="n">
-        <v>22199</v>
+        <v>21204</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>40000000</v>
+        <v>350000000</v>
       </c>
       <c r="S8" t="n">
-        <v>40000000</v>
+        <v>350000000</v>
       </c>
       <c r="T8" t="n">
-        <v>40000000</v>
+        <v>350000000</v>
       </c>
       <c r="U8" t="n">
-        <v>40000000</v>
+        <v>350000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1062500000</v>
+        <v>983250000</v>
       </c>
       <c r="S9" t="n">
-        <v>1040500000</v>
+        <v>983250000</v>
       </c>
       <c r="T9" t="n">
-        <v>1040500000</v>
+        <v>983250000</v>
       </c>
       <c r="U9" t="n">
-        <v>1040500000</v>
+        <v>983250000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1151,7 +1151,7 @@
         <v>4610</v>
       </c>
       <c r="N10" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="S10" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="T10" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="U10" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>97500000</v>
+        <v>54750000</v>
       </c>
       <c r="S11" t="n">
-        <v>97500000</v>
+        <v>54750000</v>
       </c>
       <c r="T11" t="n">
-        <v>97500000</v>
+        <v>54750000</v>
       </c>
       <c r="U11" t="n">
-        <v>97500000</v>
+        <v>54750000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1285,10 +1285,10 @@
         <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>45752420</v>
+        <v>100000000</v>
       </c>
       <c r="S12" t="n">
-        <v>42380044</v>
+        <v>100000000</v>
       </c>
       <c r="T12" t="n">
-        <v>42380044</v>
+        <v>100000000</v>
       </c>
       <c r="U12" t="n">
-        <v>42380044</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1338,36 +1338,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5121</v>
+        <v>5081</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="H13" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>3010</v>
+        <v>8009</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N13" t="n">
         <v>51000</v>
@@ -1377,30 +1377,30 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>344720630</v>
+        <v>48428689</v>
       </c>
       <c r="S13" t="n">
-        <v>222303420</v>
+        <v>43803484</v>
       </c>
       <c r="T13" t="n">
-        <v>4942214</v>
+        <v>42450254</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>42450254</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1431,16 +1431,16 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N14" t="n">
         <v>51000</v>
@@ -1455,25 +1455,25 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>40000</v>
+        <v>259985809</v>
       </c>
       <c r="S14" t="n">
-        <v>40000</v>
+        <v>1198470</v>
       </c>
       <c r="T14" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1484,30 +1484,30 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H15" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1523,30 +1523,30 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>500000</v>
+        <v>4440000</v>
       </c>
       <c r="S15" t="n">
-        <v>500000</v>
+        <v>40000</v>
       </c>
       <c r="T15" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="U15" t="n">
-        <v>500000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1557,36 +1557,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5191</v>
+        <v>5131</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G16" t="n">
         <v>122</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N16" t="n">
         <v>51000</v>
@@ -1596,30 +1596,30 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>670000</v>
+        <v>500000</v>
       </c>
       <c r="S16" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="T16" t="n">
-        <v>110000</v>
+        <v>500000</v>
       </c>
       <c r="U16" t="n">
-        <v>90000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1644,16 +1644,16 @@
         <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>6002</v>
+        <v>6011</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
         <v>4810</v>
       </c>
       <c r="N17" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>1000</v>
+        <v>243000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>180000</v>
       </c>
       <c r="T17" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="U17" t="n">
-        <v>1000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1717,16 +1717,16 @@
         <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1735,14 +1735,14 @@
         <v>4810</v>
       </c>
       <c r="N18" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>186000</v>
+        <v>1000</v>
       </c>
       <c r="S18" t="n">
         <v>1000</v>
@@ -1765,7 +1765,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -1787,25 +1787,25 @@
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N19" t="n">
         <v>51000</v>
@@ -1815,16 +1815,16 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1000</v>
+        <v>9256395</v>
       </c>
       <c r="S19" t="n">
         <v>1000</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -1849,69 +1849,69 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N20" t="n">
-        <v>12400</v>
+        <v>11101</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>23908160</v>
+        <v>1000</v>
       </c>
       <c r="S20" t="n">
-        <v>23908000</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="n">
-        <v>23908000</v>
+        <v>1000</v>
       </c>
       <c r="U20" t="n">
-        <v>23908000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -1922,58 +1922,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>694</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>8006</v>
+        <v>6001</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N21" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>600000000</v>
+        <v>1000</v>
       </c>
       <c r="S21" t="n">
-        <v>400000000</v>
+        <v>1000</v>
       </c>
       <c r="T21" t="n">
         <v>1000</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -1995,69 +1995,69 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H22" t="n">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3018</v>
+        <v>6004</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4899</v>
+        <v>4810</v>
       </c>
       <c r="N22" t="n">
-        <v>61000</v>
+        <v>12400</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>409881263</v>
+        <v>26253389</v>
       </c>
       <c r="S22" t="n">
-        <v>416795211</v>
+        <v>26254000</v>
       </c>
       <c r="T22" t="n">
-        <v>433214634</v>
+        <v>26254000</v>
       </c>
       <c r="U22" t="n">
-        <v>285354938</v>
+        <v>26254000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2068,69 +2068,69 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="H23" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
         <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>8002</v>
+        <v>8003</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N23" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4300000</v>
+        <v>250000000</v>
       </c>
       <c r="S23" t="n">
-        <v>4000000</v>
+        <v>260000000</v>
       </c>
       <c r="T23" t="n">
-        <v>3500000</v>
+        <v>1000</v>
       </c>
       <c r="U23" t="n">
-        <v>3500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2141,69 +2141,69 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="H24" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N24" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>200000</v>
+        <v>600000000</v>
       </c>
       <c r="S24" t="n">
-        <v>200000</v>
+        <v>400000000</v>
       </c>
       <c r="T24" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="U24" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2214,69 +2214,69 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5381</v>
+        <v>5251</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H25" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>8002</v>
+        <v>3018</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N25" t="n">
-        <v>11101</v>
+        <v>61000</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1000</v>
+        <v>285487805</v>
       </c>
       <c r="S25" t="n">
-        <v>1000</v>
+        <v>192101111</v>
       </c>
       <c r="T25" t="n">
-        <v>1000</v>
+        <v>279542051</v>
       </c>
       <c r="U25" t="n">
-        <v>1000</v>
+        <v>393567557</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N26" t="n">
         <v>51000</v>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4000000</v>
+        <v>5450000</v>
       </c>
       <c r="S26" t="n">
-        <v>2500000</v>
+        <v>4500000</v>
       </c>
       <c r="T26" t="n">
-        <v>2000000</v>
+        <v>4250000</v>
       </c>
       <c r="U26" t="n">
-        <v>1500000</v>
+        <v>3750000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2360,30 +2360,30 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H27" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2399,30 +2399,30 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>198940203</v>
+        <v>400000</v>
       </c>
       <c r="S27" t="n">
-        <v>224669708</v>
+        <v>400000</v>
       </c>
       <c r="T27" t="n">
-        <v>92100648</v>
+        <v>400000</v>
       </c>
       <c r="U27" t="n">
-        <v>13570642</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2433,69 +2433,69 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H28" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>3005</v>
+        <v>8002</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N28" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>241821909</v>
+        <v>1000</v>
       </c>
       <c r="S28" t="n">
-        <v>515862966</v>
+        <v>1000</v>
       </c>
       <c r="T28" t="n">
-        <v>537405240</v>
+        <v>1000</v>
       </c>
       <c r="U28" t="n">
-        <v>480353203</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2506,36 +2506,36 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H29" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>3006</v>
+        <v>8002</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N29" t="n">
         <v>51000</v>
@@ -2545,30 +2545,30 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>30805275</v>
+        <v>4000000</v>
       </c>
       <c r="S29" t="n">
-        <v>15389442</v>
+        <v>5250000</v>
       </c>
       <c r="T29" t="n">
-        <v>4894000</v>
+        <v>5750000</v>
       </c>
       <c r="U29" t="n">
-        <v>25171936</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2593,16 +2593,16 @@
         <v>752</v>
       </c>
       <c r="H30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>3001</v>
+        <v>3004</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2618,30 +2618,30 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>49096963</v>
+        <v>231539977</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>366611726</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>234560000</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>83098000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -2666,16 +2666,16 @@
         <v>752</v>
       </c>
       <c r="H31" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I31" t="n">
         <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2691,30 +2691,30 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>130600000</v>
+        <v>216613767</v>
       </c>
       <c r="S31" t="n">
-        <v>174928000</v>
+        <v>863139747</v>
       </c>
       <c r="T31" t="n">
-        <v>139546000</v>
+        <v>669563561</v>
       </c>
       <c r="U31" t="n">
-        <v>125024000</v>
+        <v>481331764</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
@@ -2739,16 +2739,16 @@
         <v>752</v>
       </c>
       <c r="H32" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2764,30 +2764,30 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>13194360</v>
+        <v>42479000</v>
       </c>
       <c r="S32" t="n">
-        <v>8683890</v>
+        <v>9806000</v>
       </c>
       <c r="T32" t="n">
-        <v>13879558</v>
+        <v>13975000</v>
       </c>
       <c r="U32" t="n">
-        <v>70075101</v>
+        <v>7469000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
@@ -2812,16 +2812,16 @@
         <v>752</v>
       </c>
       <c r="H33" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I33" t="n">
         <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>3014</v>
+        <v>3009</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2837,30 +2837,30 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>508846661</v>
+        <v>92271447</v>
       </c>
       <c r="S33" t="n">
-        <v>2115585319</v>
+        <v>77871808</v>
       </c>
       <c r="T33" t="n">
-        <v>511690078</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>119701000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
@@ -2871,11 +2871,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2885,16 +2885,16 @@
         <v>752</v>
       </c>
       <c r="H34" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2910,30 +2910,30 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>3487433034</v>
+        <v>100000</v>
       </c>
       <c r="S34" t="n">
-        <v>3930724350</v>
+        <v>338387000</v>
       </c>
       <c r="T34" t="n">
-        <v>4329558721</v>
+        <v>416585000</v>
       </c>
       <c r="U34" t="n">
-        <v>3703598493</v>
+        <v>149872000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
@@ -2944,11 +2944,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2958,16 +2958,16 @@
         <v>752</v>
       </c>
       <c r="H35" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>247223810</v>
+        <v>96218712</v>
       </c>
       <c r="S35" t="n">
-        <v>224139298</v>
+        <v>137689405</v>
       </c>
       <c r="T35" t="n">
-        <v>143327686</v>
+        <v>98836755</v>
       </c>
       <c r="U35" t="n">
-        <v>188131849</v>
+        <v>26593000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
@@ -3017,30 +3017,30 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H36" t="n">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>6012</v>
+        <v>3008</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3056,30 +3056,30 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>2000000</v>
+        <v>18091000</v>
       </c>
       <c r="S36" t="n">
-        <v>2000000</v>
+        <v>17663000</v>
       </c>
       <c r="T36" t="n">
-        <v>2000000</v>
+        <v>76813000</v>
       </c>
       <c r="U36" t="n">
-        <v>2000000</v>
+        <v>12986000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
@@ -3090,36 +3090,36 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G37" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H37" t="n">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>8012</v>
+        <v>3014</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N37" t="n">
         <v>51000</v>
@@ -3129,137 +3129,137 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>45000000</v>
+        <v>190392082</v>
       </c>
       <c r="S37" t="n">
-        <v>45000000</v>
+        <v>2427753697</v>
       </c>
       <c r="T37" t="n">
-        <v>45000000</v>
+        <v>2814753453</v>
       </c>
       <c r="U37" t="n">
-        <v>45000000</v>
+        <v>2447200992</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B38" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5261</v>
+        <v>5401</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="H38" t="n">
-        <v>705</v>
+        <v>72</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>8011</v>
+        <v>3002</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N38" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>1000</v>
+        <v>4721877188</v>
       </c>
       <c r="S38" t="n">
-        <v>1000</v>
+        <v>5072587431</v>
       </c>
       <c r="T38" t="n">
-        <v>1000</v>
+        <v>4781108423</v>
       </c>
       <c r="U38" t="n">
-        <v>1000</v>
+        <v>4605781325</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B39" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5141</v>
+        <v>5401</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G39" t="n">
-        <v>126</v>
+        <v>752</v>
       </c>
       <c r="H39" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>6006</v>
+        <v>3003</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3275,70 +3275,70 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>3280000</v>
+        <v>247976000</v>
       </c>
       <c r="S39" t="n">
-        <v>13250000</v>
+        <v>195928000</v>
       </c>
       <c r="T39" t="n">
-        <v>6250000</v>
+        <v>223404000</v>
       </c>
       <c r="U39" t="n">
-        <v>3250000</v>
+        <v>76152000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B40" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="H40" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>8001</v>
+        <v>6012</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N40" t="n">
         <v>51000</v>
@@ -3348,24 +3348,316 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5511</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>17</v>
+      </c>
+      <c r="G41" t="n">
+        <v>512</v>
+      </c>
+      <c r="H41" t="n">
+        <v>21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8012</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N41" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="T41" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="U41" t="n">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5261</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>26</v>
+      </c>
+      <c r="G42" t="n">
+        <v>783</v>
+      </c>
+      <c r="H42" t="n">
+        <v>705</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8011</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4510</v>
+      </c>
+      <c r="N42" t="n">
+        <v>11101</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" t="n">
+        <v>126</v>
+      </c>
+      <c r="H43" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6006</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N43" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>13233200</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>126</v>
+      </c>
+      <c r="H44" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>4810</v>
+      </c>
+      <c r="N44" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>35386354</v>
-      </c>
-      <c r="S40" t="n">
-        <v>39030861</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="R44" t="n">
+        <v>38099783</v>
+      </c>
+      <c r="S44" t="n">
         <v>31646705</v>
       </c>
-      <c r="U40" t="n">
+      <c r="T44" t="n">
+        <v>26305815</v>
+      </c>
+      <c r="U44" t="n">
         <v>26305815</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="S9" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="T9" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="U9" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="10">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="T10" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="U10" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="S11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="T11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="U11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="S12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="T12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="U12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
     </row>
     <row r="13">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="S9" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="T9" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
       <c r="U9" t="n">
-        <v>40000000</v>
+        <v>983250000</v>
       </c>
     </row>
     <row r="10">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="S10" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="T10" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
       <c r="U10" t="n">
-        <v>983250000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="S11" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="T11" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="U11" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
     </row>
     <row r="12">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="S12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="T12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="U12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="S11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="T11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="U11" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="12">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="S12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="T12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
       <c r="U12" t="n">
-        <v>100000000</v>
+        <v>54750000</v>
       </c>
     </row>
     <row r="13">

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -503,28 +503,28 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2025</t>
+          <t>VALOR (R$) 2026</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2026</t>
+          <t>VALOR (R$) 2027</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2027</t>
+          <t>VALOR (R$) 2028</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2028</t>
+          <t>VALOR (R$) 2029</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -656,21 +656,21 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6380000</v>
+        <v>4655000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>7777327</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -729,21 +729,21 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>6240000</v>
+        <v>3500000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -838,19 +838,19 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>6009</v>
+        <v>3012</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -859,37 +859,37 @@
         <v>4610</v>
       </c>
       <c r="N6" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>50000000</v>
+        <v>5000000</v>
       </c>
       <c r="S6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -932,7 +932,7 @@
         <v>4610</v>
       </c>
       <c r="N7" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -990,13 +990,13 @@
         <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>8008</v>
+        <v>6009</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>4610</v>
       </c>
       <c r="N8" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="S8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="T8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="U8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1078,7 +1078,7 @@
         <v>4610</v>
       </c>
       <c r="N9" t="n">
-        <v>22199</v>
+        <v>21204</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="S9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="T9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="U9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="T10" t="n">
-        <v>40000000</v>
+        <v>2710000000</v>
       </c>
       <c r="U10" t="n">
-        <v>40000000</v>
+        <v>2810000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1224,7 +1224,7 @@
         <v>4610</v>
       </c>
       <c r="N11" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>54750000</v>
+        <v>40000000</v>
       </c>
       <c r="S11" t="n">
-        <v>54750000</v>
+        <v>40000000</v>
       </c>
       <c r="T11" t="n">
-        <v>54750000</v>
+        <v>40000000</v>
       </c>
       <c r="U11" t="n">
-        <v>54750000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1319,15 +1319,15 @@
         <v>100000000</v>
       </c>
       <c r="T12" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="U12" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1358,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1382,25 +1382,25 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>48428689</v>
+        <v>95000000</v>
       </c>
       <c r="S13" t="n">
-        <v>43803484</v>
+        <v>100000000</v>
       </c>
       <c r="T13" t="n">
-        <v>42450254</v>
+        <v>100000000</v>
       </c>
       <c r="U13" t="n">
-        <v>42450254</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1411,36 +1411,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5121</v>
+        <v>5081</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>3010</v>
+        <v>8009</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N14" t="n">
         <v>51000</v>
@@ -1450,22 +1450,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>259985809</v>
+        <v>55500000</v>
       </c>
       <c r="S14" t="n">
-        <v>1198470</v>
+        <v>55500000</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>55500000</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1504,16 +1504,16 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N15" t="n">
         <v>51000</v>
@@ -1528,25 +1528,25 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>4440000</v>
+        <v>70784312</v>
       </c>
       <c r="S15" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1557,30 +1557,30 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H16" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1596,30 +1596,30 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>500000</v>
+        <v>2347000</v>
       </c>
       <c r="S16" t="n">
-        <v>500000</v>
+        <v>5282000</v>
       </c>
       <c r="T16" t="n">
-        <v>500000</v>
+        <v>9124000</v>
       </c>
       <c r="U16" t="n">
-        <v>500000</v>
+        <v>4492000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1630,36 +1630,36 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5191</v>
+        <v>5131</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N17" t="n">
         <v>51000</v>
@@ -1669,30 +1669,30 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>243000</v>
+        <v>250000</v>
       </c>
       <c r="S17" t="n">
-        <v>180000</v>
+        <v>500000</v>
       </c>
       <c r="T17" t="n">
-        <v>120000</v>
+        <v>500000</v>
       </c>
       <c r="U17" t="n">
-        <v>60000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1717,16 +1717,16 @@
         <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>6003</v>
+        <v>6011</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1735,37 +1735,37 @@
         <v>4810</v>
       </c>
       <c r="N18" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1000</v>
+        <v>240000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>180000</v>
       </c>
       <c r="T18" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="U18" t="n">
-        <v>1000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -1808,7 +1808,7 @@
         <v>4810</v>
       </c>
       <c r="N19" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>9256395</v>
+        <v>1000</v>
       </c>
       <c r="S19" t="n">
         <v>1000</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -1860,44 +1860,44 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N20" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1000</v>
+        <v>1461000</v>
       </c>
       <c r="S20" t="n">
         <v>1000</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -1954,7 +1954,7 @@
         <v>4510</v>
       </c>
       <c r="N21" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -1995,69 +1995,69 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I22" t="n">
         <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N22" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>26253389</v>
+        <v>1000</v>
       </c>
       <c r="S22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
       <c r="T22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
       <c r="U22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2079,19 +2079,19 @@
         <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>694</v>
+        <v>122</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>8003</v>
+        <v>6004</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2107,30 +2107,30 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>250000000</v>
+        <v>30022403</v>
       </c>
       <c r="S23" t="n">
-        <v>260000000</v>
+        <v>30000000</v>
       </c>
       <c r="T23" t="n">
-        <v>1000</v>
+        <v>30000000</v>
       </c>
       <c r="U23" t="n">
-        <v>1000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2155,16 +2155,16 @@
         <v>694</v>
       </c>
       <c r="H24" t="n">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>8006</v>
+        <v>8003</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2180,30 +2180,30 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>600000000</v>
+        <v>250000000</v>
       </c>
       <c r="S24" t="n">
-        <v>400000000</v>
+        <v>260000000</v>
       </c>
       <c r="T24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2214,69 +2214,69 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>121</v>
+        <v>694</v>
       </c>
       <c r="H25" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>3018</v>
+        <v>8004</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N25" t="n">
-        <v>61000</v>
+        <v>12400</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>285487805</v>
+        <v>500000000</v>
       </c>
       <c r="S25" t="n">
-        <v>192101111</v>
+        <v>325000000</v>
       </c>
       <c r="T25" t="n">
-        <v>279542051</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>393567557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2287,69 +2287,69 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="H26" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="I26" t="n">
         <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N26" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>5450000</v>
+        <v>600000000</v>
       </c>
       <c r="S26" t="n">
-        <v>4500000</v>
+        <v>400000000</v>
       </c>
       <c r="T26" t="n">
-        <v>4250000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3750000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2360,36 +2360,36 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5381</v>
+        <v>5251</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H27" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>8002</v>
+        <v>3018</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N27" t="n">
         <v>51000</v>
@@ -2399,30 +2399,30 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>400000</v>
+        <v>191687487</v>
       </c>
       <c r="S27" t="n">
-        <v>400000</v>
+        <v>300208631</v>
       </c>
       <c r="T27" t="n">
-        <v>400000</v>
+        <v>418281042</v>
       </c>
       <c r="U27" t="n">
-        <v>400000</v>
+        <v>279308416</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2462,10 +2462,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N28" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2481,21 +2481,21 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>1000</v>
+        <v>9152200</v>
       </c>
       <c r="S28" t="n">
-        <v>1000</v>
+        <v>4250000</v>
       </c>
       <c r="T28" t="n">
-        <v>1000</v>
+        <v>3750000</v>
       </c>
       <c r="U28" t="n">
-        <v>1000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N29" t="n">
         <v>51000</v>
@@ -2554,21 +2554,21 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4000000</v>
+        <v>522300</v>
       </c>
       <c r="S29" t="n">
-        <v>5250000</v>
+        <v>400000</v>
       </c>
       <c r="T29" t="n">
-        <v>5750000</v>
+        <v>400000</v>
       </c>
       <c r="U29" t="n">
-        <v>6000000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2579,69 +2579,69 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H30" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N30" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>231539977</v>
+        <v>1000</v>
       </c>
       <c r="S30" t="n">
-        <v>366611726</v>
+        <v>1000</v>
       </c>
       <c r="T30" t="n">
-        <v>234560000</v>
+        <v>1000</v>
       </c>
       <c r="U30" t="n">
-        <v>83098000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -2652,36 +2652,36 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H31" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>3005</v>
+        <v>8002</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N31" t="n">
         <v>51000</v>
@@ -2691,30 +2691,30 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>216613767</v>
+        <v>12880000</v>
       </c>
       <c r="S31" t="n">
-        <v>863139747</v>
+        <v>4350000</v>
       </c>
       <c r="T31" t="n">
-        <v>669563561</v>
+        <v>3850000</v>
       </c>
       <c r="U31" t="n">
-        <v>481331764</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
@@ -2745,10 +2745,10 @@
         <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2769,25 +2769,25 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>42479000</v>
+        <v>343756125</v>
       </c>
       <c r="S32" t="n">
-        <v>9806000</v>
+        <v>362356106</v>
       </c>
       <c r="T32" t="n">
-        <v>13975000</v>
+        <v>147414569</v>
       </c>
       <c r="U32" t="n">
-        <v>7469000</v>
+        <v>54954</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
@@ -2818,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N33" t="n">
         <v>51000</v>
@@ -2842,25 +2842,25 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>92271447</v>
+        <v>285714873</v>
       </c>
       <c r="S33" t="n">
-        <v>77871808</v>
+        <v>667922000</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>681702031</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>151210212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
@@ -2885,16 +2885,16 @@
         <v>752</v>
       </c>
       <c r="H34" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2910,30 +2910,30 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>100000</v>
+        <v>65874000</v>
       </c>
       <c r="S34" t="n">
-        <v>338387000</v>
+        <v>22981000</v>
       </c>
       <c r="T34" t="n">
-        <v>416585000</v>
+        <v>16749000</v>
       </c>
       <c r="U34" t="n">
-        <v>149872000</v>
+        <v>10040000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
@@ -2958,22 +2958,22 @@
         <v>752</v>
       </c>
       <c r="H35" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>3007</v>
+        <v>3009</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N35" t="n">
         <v>51000</v>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>96218712</v>
+        <v>8146743</v>
       </c>
       <c r="S35" t="n">
-        <v>137689405</v>
+        <v>90753826</v>
       </c>
       <c r="T35" t="n">
-        <v>98836755</v>
+        <v>75223990</v>
       </c>
       <c r="U35" t="n">
-        <v>26593000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
@@ -3037,10 +3037,10 @@
         <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>3008</v>
+        <v>3001</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3061,25 +3061,25 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>18091000</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>17663000</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>76813000</v>
+        <v>460000000</v>
       </c>
       <c r="U36" t="n">
-        <v>12986000</v>
+        <v>700000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
@@ -3110,16 +3110,16 @@
         <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N37" t="n">
         <v>51000</v>
@@ -3134,25 +3134,25 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>190392082</v>
+        <v>65661789</v>
       </c>
       <c r="S37" t="n">
-        <v>2427753697</v>
+        <v>248798436</v>
       </c>
       <c r="T37" t="n">
-        <v>2814753453</v>
+        <v>235222147</v>
       </c>
       <c r="U37" t="n">
-        <v>2447200992</v>
+        <v>129088019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="n">
         <v>1220</v>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3177,16 +3177,16 @@
         <v>752</v>
       </c>
       <c r="H38" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I38" t="n">
         <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3202,30 +3202,30 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4721877188</v>
+        <v>42279000</v>
       </c>
       <c r="S38" t="n">
-        <v>5072587431</v>
+        <v>25196000</v>
       </c>
       <c r="T38" t="n">
-        <v>4781108423</v>
+        <v>34638000</v>
       </c>
       <c r="U38" t="n">
-        <v>4605781325</v>
+        <v>14426000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="n">
         <v>1220</v>
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3250,22 +3250,22 @@
         <v>752</v>
       </c>
       <c r="H39" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I39" t="n">
         <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>3003</v>
+        <v>3014</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N39" t="n">
         <v>51000</v>
@@ -3275,30 +3275,30 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>247976000</v>
+        <v>116689303</v>
       </c>
       <c r="S39" t="n">
-        <v>195928000</v>
+        <v>1836775844</v>
       </c>
       <c r="T39" t="n">
-        <v>223404000</v>
+        <v>1978096688</v>
       </c>
       <c r="U39" t="n">
-        <v>76152000</v>
+        <v>1952010335</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="n">
         <v>1220</v>
@@ -3309,30 +3309,30 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>6012</v>
+        <v>3002</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3348,30 +3348,30 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>2000000</v>
+        <v>5072587386</v>
       </c>
       <c r="S40" t="n">
-        <v>2000000</v>
+        <v>4758143083</v>
       </c>
       <c r="T40" t="n">
-        <v>2000000</v>
+        <v>4688703167</v>
       </c>
       <c r="U40" t="n">
-        <v>2000000</v>
+        <v>4735443098</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="n">
         <v>1220</v>
@@ -3382,30 +3382,30 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H41" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>8012</v>
+        <v>3003</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3421,137 +3421,137 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>45000000</v>
+        <v>233275000</v>
       </c>
       <c r="S41" t="n">
-        <v>45000000</v>
+        <v>231383000</v>
       </c>
       <c r="T41" t="n">
-        <v>45000000</v>
+        <v>237131000</v>
       </c>
       <c r="U41" t="n">
-        <v>45000000</v>
+        <v>122592000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5261</v>
+        <v>5511</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>783</v>
+        <v>512</v>
       </c>
       <c r="H42" t="n">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>8011</v>
+        <v>6012</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N42" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="S42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="T42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="U42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G43" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="H43" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>6006</v>
+        <v>8012</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3567,70 +3567,70 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>13233200</v>
+        <v>30000000</v>
       </c>
       <c r="S43" t="n">
-        <v>6250000</v>
+        <v>30000000</v>
       </c>
       <c r="T43" t="n">
-        <v>3250000</v>
+        <v>30000000</v>
       </c>
       <c r="U43" t="n">
-        <v>3250000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="H44" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I44" t="n">
         <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>8001</v>
+        <v>8012</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N44" t="n">
         <v>51000</v>
@@ -3640,25 +3640,317 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="T44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>5511</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>17</v>
+      </c>
+      <c r="G45" t="n">
+        <v>512</v>
+      </c>
+      <c r="H45" t="n">
+        <v>21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8012</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N45" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5261</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>783</v>
+      </c>
+      <c r="H46" t="n">
+        <v>705</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8011</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4510</v>
+      </c>
+      <c r="N46" t="n">
+        <v>11101</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>126</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6006</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N47" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>23614000</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>126</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8001</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4810</v>
+      </c>
+      <c r="N48" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>38099783</v>
-      </c>
-      <c r="S44" t="n">
-        <v>31646705</v>
-      </c>
-      <c r="T44" t="n">
+      <c r="R48" t="n">
+        <v>20445642</v>
+      </c>
+      <c r="S48" t="n">
         <v>26305815</v>
       </c>
-      <c r="U44" t="n">
+      <c r="T48" t="n">
         <v>26305815</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6210000</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -503,28 +503,28 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2025</t>
+          <t>VALOR (R$) 2026</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2026</t>
+          <t>VALOR (R$) 2027</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2027</t>
+          <t>VALOR (R$) 2028</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>VALOR (R$) 2028</t>
+          <t>VALOR (R$) 2029</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -656,21 +656,21 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6380000</v>
+        <v>4655000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>7777327</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -729,21 +729,21 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>6240000</v>
+        <v>3500000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -838,19 +838,19 @@
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>6009</v>
+        <v>3012</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -859,37 +859,37 @@
         <v>4610</v>
       </c>
       <c r="N6" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>50000000</v>
+        <v>5000000</v>
       </c>
       <c r="S6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -932,7 +932,7 @@
         <v>4610</v>
       </c>
       <c r="N7" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -990,13 +990,13 @@
         <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>8008</v>
+        <v>6009</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>4610</v>
       </c>
       <c r="N8" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="S8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="T8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
       <c r="U8" t="n">
-        <v>350000000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1078,7 +1078,7 @@
         <v>4610</v>
       </c>
       <c r="N9" t="n">
-        <v>22199</v>
+        <v>21204</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="S9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="T9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="U9" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="S10" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="T10" t="n">
-        <v>40000000</v>
+        <v>2710000000</v>
       </c>
       <c r="U10" t="n">
-        <v>40000000</v>
+        <v>2810000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1224,7 +1224,7 @@
         <v>4610</v>
       </c>
       <c r="N11" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="S11" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="T11" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
       <c r="U11" t="n">
-        <v>100000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="S12" t="n">
-        <v>54750000</v>
+        <v>100000000</v>
       </c>
       <c r="T12" t="n">
-        <v>54750000</v>
+        <v>200000000</v>
       </c>
       <c r="U12" t="n">
-        <v>54750000</v>
+        <v>200000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1358,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1382,25 +1382,25 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>48428689</v>
+        <v>95000000</v>
       </c>
       <c r="S13" t="n">
-        <v>43803484</v>
+        <v>100000000</v>
       </c>
       <c r="T13" t="n">
-        <v>42450254</v>
+        <v>100000000</v>
       </c>
       <c r="U13" t="n">
-        <v>42450254</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1411,36 +1411,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5121</v>
+        <v>5081</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>3010</v>
+        <v>8009</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N14" t="n">
         <v>51000</v>
@@ -1450,22 +1450,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>259985809</v>
+        <v>55500000</v>
       </c>
       <c r="S14" t="n">
-        <v>1198470</v>
+        <v>55500000</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>55500000</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1504,16 +1504,16 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N15" t="n">
         <v>51000</v>
@@ -1528,25 +1528,25 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>4440000</v>
+        <v>70784312</v>
       </c>
       <c r="S15" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1557,30 +1557,30 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="H16" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1596,30 +1596,30 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>500000</v>
+        <v>2347000</v>
       </c>
       <c r="S16" t="n">
-        <v>500000</v>
+        <v>5282000</v>
       </c>
       <c r="T16" t="n">
-        <v>500000</v>
+        <v>9124000</v>
       </c>
       <c r="U16" t="n">
-        <v>500000</v>
+        <v>4492000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1630,36 +1630,36 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5191</v>
+        <v>5131</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>122</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N17" t="n">
         <v>51000</v>
@@ -1669,30 +1669,30 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>243000</v>
+        <v>250000</v>
       </c>
       <c r="S17" t="n">
-        <v>180000</v>
+        <v>500000</v>
       </c>
       <c r="T17" t="n">
-        <v>120000</v>
+        <v>500000</v>
       </c>
       <c r="U17" t="n">
-        <v>60000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1717,16 +1717,16 @@
         <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>6003</v>
+        <v>6011</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1735,37 +1735,37 @@
         <v>4810</v>
       </c>
       <c r="N18" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1000</v>
+        <v>240000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>180000</v>
       </c>
       <c r="T18" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="U18" t="n">
-        <v>1000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -1808,7 +1808,7 @@
         <v>4810</v>
       </c>
       <c r="N19" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>9256395</v>
+        <v>1000</v>
       </c>
       <c r="S19" t="n">
         <v>1000</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -1860,44 +1860,44 @@
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4510</v>
+        <v>4810</v>
       </c>
       <c r="N20" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1000</v>
+        <v>1461000</v>
       </c>
       <c r="S20" t="n">
         <v>1000</v>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -1954,7 +1954,7 @@
         <v>4510</v>
       </c>
       <c r="N21" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -1995,69 +1995,69 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I22" t="n">
         <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4810</v>
+        <v>4510</v>
       </c>
       <c r="N22" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>26253389</v>
+        <v>1000</v>
       </c>
       <c r="S22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
       <c r="T22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
       <c r="U22" t="n">
-        <v>26254000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2079,19 +2079,19 @@
         <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>694</v>
+        <v>122</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>8003</v>
+        <v>6004</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2107,30 +2107,30 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>250000000</v>
+        <v>30022403</v>
       </c>
       <c r="S23" t="n">
-        <v>260000000</v>
+        <v>30000000</v>
       </c>
       <c r="T23" t="n">
-        <v>1000</v>
+        <v>30000000</v>
       </c>
       <c r="U23" t="n">
-        <v>1000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2155,16 +2155,16 @@
         <v>694</v>
       </c>
       <c r="H24" t="n">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>8006</v>
+        <v>8003</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2180,30 +2180,30 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>600000000</v>
+        <v>250000000</v>
       </c>
       <c r="S24" t="n">
-        <v>400000000</v>
+        <v>260000000</v>
       </c>
       <c r="T24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2214,69 +2214,69 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>121</v>
+        <v>694</v>
       </c>
       <c r="H25" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>3018</v>
+        <v>8004</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N25" t="n">
-        <v>61000</v>
+        <v>12400</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>285487805</v>
+        <v>500000000</v>
       </c>
       <c r="S25" t="n">
-        <v>192101111</v>
+        <v>325000000</v>
       </c>
       <c r="T25" t="n">
-        <v>279542051</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>393567557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2287,69 +2287,69 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="H26" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="I26" t="n">
         <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N26" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>5450000</v>
+        <v>600000000</v>
       </c>
       <c r="S26" t="n">
-        <v>4500000</v>
+        <v>400000000</v>
       </c>
       <c r="T26" t="n">
-        <v>4250000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3750000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2360,36 +2360,36 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5381</v>
+        <v>5251</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H27" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>8002</v>
+        <v>3018</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N27" t="n">
         <v>51000</v>
@@ -2399,30 +2399,30 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>400000</v>
+        <v>191687487</v>
       </c>
       <c r="S27" t="n">
-        <v>400000</v>
+        <v>300208631</v>
       </c>
       <c r="T27" t="n">
-        <v>400000</v>
+        <v>418281042</v>
       </c>
       <c r="U27" t="n">
-        <v>400000</v>
+        <v>279308416</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2462,10 +2462,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N28" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2481,21 +2481,21 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>1000</v>
+        <v>9152200</v>
       </c>
       <c r="S28" t="n">
-        <v>1000</v>
+        <v>4250000</v>
       </c>
       <c r="T28" t="n">
-        <v>1000</v>
+        <v>3750000</v>
       </c>
       <c r="U28" t="n">
-        <v>1000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N29" t="n">
         <v>51000</v>
@@ -2554,21 +2554,21 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4000000</v>
+        <v>522300</v>
       </c>
       <c r="S29" t="n">
-        <v>5250000</v>
+        <v>400000</v>
       </c>
       <c r="T29" t="n">
-        <v>5750000</v>
+        <v>400000</v>
       </c>
       <c r="U29" t="n">
-        <v>6000000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2579,69 +2579,69 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H30" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N30" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>231539977</v>
+        <v>1000</v>
       </c>
       <c r="S30" t="n">
-        <v>366611726</v>
+        <v>1000</v>
       </c>
       <c r="T30" t="n">
-        <v>234560000</v>
+        <v>1000</v>
       </c>
       <c r="U30" t="n">
-        <v>83098000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -2652,36 +2652,36 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="H31" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>3005</v>
+        <v>8002</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4610</v>
+        <v>4810</v>
       </c>
       <c r="N31" t="n">
         <v>51000</v>
@@ -2691,30 +2691,30 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>216613767</v>
+        <v>12880000</v>
       </c>
       <c r="S31" t="n">
-        <v>863139747</v>
+        <v>4350000</v>
       </c>
       <c r="T31" t="n">
-        <v>669563561</v>
+        <v>3850000</v>
       </c>
       <c r="U31" t="n">
-        <v>481331764</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
@@ -2745,10 +2745,10 @@
         <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2769,25 +2769,25 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>42479000</v>
+        <v>343756125</v>
       </c>
       <c r="S32" t="n">
-        <v>9806000</v>
+        <v>362356106</v>
       </c>
       <c r="T32" t="n">
-        <v>13975000</v>
+        <v>147414569</v>
       </c>
       <c r="U32" t="n">
-        <v>7469000</v>
+        <v>54954</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
@@ -2818,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N33" t="n">
         <v>51000</v>
@@ -2842,25 +2842,25 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>92271447</v>
+        <v>285714873</v>
       </c>
       <c r="S33" t="n">
-        <v>77871808</v>
+        <v>667922000</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>681702031</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>151210212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
@@ -2885,16 +2885,16 @@
         <v>752</v>
       </c>
       <c r="H34" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2910,30 +2910,30 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>100000</v>
+        <v>65874000</v>
       </c>
       <c r="S34" t="n">
-        <v>338387000</v>
+        <v>22981000</v>
       </c>
       <c r="T34" t="n">
-        <v>416585000</v>
+        <v>16749000</v>
       </c>
       <c r="U34" t="n">
-        <v>149872000</v>
+        <v>10040000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
@@ -2958,22 +2958,22 @@
         <v>752</v>
       </c>
       <c r="H35" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>3007</v>
+        <v>3009</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N35" t="n">
         <v>51000</v>
@@ -2983,30 +2983,30 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>96218712</v>
+        <v>8146743</v>
       </c>
       <c r="S35" t="n">
-        <v>137689405</v>
+        <v>90753826</v>
       </c>
       <c r="T35" t="n">
-        <v>98836755</v>
+        <v>75223990</v>
       </c>
       <c r="U35" t="n">
-        <v>26593000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
@@ -3037,10 +3037,10 @@
         <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>3008</v>
+        <v>3001</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3061,25 +3061,25 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>18091000</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>17663000</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>76813000</v>
+        <v>460000000</v>
       </c>
       <c r="U36" t="n">
-        <v>12986000</v>
+        <v>700000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
@@ -3110,16 +3110,16 @@
         <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N37" t="n">
         <v>51000</v>
@@ -3134,25 +3134,25 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>190392082</v>
+        <v>65661789</v>
       </c>
       <c r="S37" t="n">
-        <v>2427753697</v>
+        <v>248798436</v>
       </c>
       <c r="T37" t="n">
-        <v>2814753453</v>
+        <v>235222147</v>
       </c>
       <c r="U37" t="n">
-        <v>2447200992</v>
+        <v>129088019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="n">
         <v>1220</v>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3177,16 +3177,16 @@
         <v>752</v>
       </c>
       <c r="H38" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I38" t="n">
         <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3202,30 +3202,30 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4721877188</v>
+        <v>42279000</v>
       </c>
       <c r="S38" t="n">
-        <v>5072587431</v>
+        <v>25196000</v>
       </c>
       <c r="T38" t="n">
-        <v>4781108423</v>
+        <v>34638000</v>
       </c>
       <c r="U38" t="n">
-        <v>4605781325</v>
+        <v>14426000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="n">
         <v>1220</v>
@@ -3236,11 +3236,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3250,22 +3250,22 @@
         <v>752</v>
       </c>
       <c r="H39" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="I39" t="n">
         <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>3003</v>
+        <v>3014</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4610</v>
+        <v>4510</v>
       </c>
       <c r="N39" t="n">
         <v>51000</v>
@@ -3275,30 +3275,30 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>247976000</v>
+        <v>116689303</v>
       </c>
       <c r="S39" t="n">
-        <v>195928000</v>
+        <v>1836775844</v>
       </c>
       <c r="T39" t="n">
-        <v>223404000</v>
+        <v>1978096688</v>
       </c>
       <c r="U39" t="n">
-        <v>76152000</v>
+        <v>1952010335</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="n">
         <v>1220</v>
@@ -3309,30 +3309,30 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>6012</v>
+        <v>3002</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3348,30 +3348,30 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>2000000</v>
+        <v>5072587386</v>
       </c>
       <c r="S40" t="n">
-        <v>2000000</v>
+        <v>4758143083</v>
       </c>
       <c r="T40" t="n">
-        <v>2000000</v>
+        <v>4688703167</v>
       </c>
       <c r="U40" t="n">
-        <v>2000000</v>
+        <v>4735443098</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="n">
         <v>1220</v>
@@ -3382,30 +3382,30 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="H41" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>8012</v>
+        <v>3003</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3421,137 +3421,137 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>45000000</v>
+        <v>233275000</v>
       </c>
       <c r="S41" t="n">
-        <v>45000000</v>
+        <v>231383000</v>
       </c>
       <c r="T41" t="n">
-        <v>45000000</v>
+        <v>237131000</v>
       </c>
       <c r="U41" t="n">
-        <v>45000000</v>
+        <v>122592000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5261</v>
+        <v>5511</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>783</v>
+        <v>512</v>
       </c>
       <c r="H42" t="n">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>8011</v>
+        <v>6012</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="N42" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="S42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="T42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="U42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G43" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="H43" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>6006</v>
+        <v>8012</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3567,70 +3567,70 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>13233200</v>
+        <v>30000000</v>
       </c>
       <c r="S43" t="n">
-        <v>6250000</v>
+        <v>30000000</v>
       </c>
       <c r="T43" t="n">
-        <v>3250000</v>
+        <v>30000000</v>
       </c>
       <c r="U43" t="n">
-        <v>3250000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="H44" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I44" t="n">
         <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>8001</v>
+        <v>8012</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4810</v>
+        <v>4610</v>
       </c>
       <c r="N44" t="n">
         <v>51000</v>
@@ -3640,25 +3640,317 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="T44" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>5511</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>17</v>
+      </c>
+      <c r="G45" t="n">
+        <v>512</v>
+      </c>
+      <c r="H45" t="n">
+        <v>21</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8012</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N45" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="U45" t="n">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5261</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>783</v>
+      </c>
+      <c r="H46" t="n">
+        <v>705</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8011</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4510</v>
+      </c>
+      <c r="N46" t="n">
+        <v>11101</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>126</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6006</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4610</v>
+      </c>
+      <c r="N47" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>23614000</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3250000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5141</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>126</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8001</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4810</v>
+      </c>
+      <c r="N48" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>38099783</v>
-      </c>
-      <c r="S44" t="n">
-        <v>31646705</v>
-      </c>
-      <c r="T44" t="n">
+      <c r="R48" t="n">
+        <v>20445642</v>
+      </c>
+      <c r="S48" t="n">
         <v>26305815</v>
       </c>
-      <c r="U44" t="n">
+      <c r="T48" t="n">
         <v>26305815</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6210000</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
+++ b/bancos/SISOR/BASE_QDD_PLURIANUAL_INVEST.xlsx
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2510000000</v>
+        <v>40000000</v>
       </c>
       <c r="S10" t="n">
-        <v>2510000000</v>
+        <v>40000000</v>
       </c>
       <c r="T10" t="n">
-        <v>2710000000</v>
+        <v>40000000</v>
       </c>
       <c r="U10" t="n">
-        <v>2810000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="S11" t="n">
-        <v>40000000</v>
+        <v>2510000000</v>
       </c>
       <c r="T11" t="n">
-        <v>40000000</v>
+        <v>2710000000</v>
       </c>
       <c r="U11" t="n">
-        <v>40000000</v>
+        <v>2810000000</v>
       </c>
     </row>
     <row r="12">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>100000000</v>
+        <v>95000000</v>
       </c>
       <c r="S12" t="n">
         <v>100000000</v>
       </c>
       <c r="T12" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="U12" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13">
@@ -1386,16 +1386,16 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>95000000</v>
+        <v>100000000</v>
       </c>
       <c r="S13" t="n">
         <v>100000000</v>
       </c>
       <c r="T13" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="U13" t="n">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
     </row>
     <row r="14">
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
       <c r="S43" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
       <c r="T43" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
       <c r="U43" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="44">
@@ -3649,16 +3649,16 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>10000000</v>
+        <v>30000000</v>
       </c>
       <c r="S44" t="n">
-        <v>10000000</v>
+        <v>30000000</v>
       </c>
       <c r="T44" t="n">
-        <v>10000000</v>
+        <v>30000000</v>
       </c>
       <c r="U44" t="n">
-        <v>10000000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="45">
